--- a/data/Publication details.xlsx
+++ b/data/Publication details.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10222"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/conorisco/Dropbox (Personal)/Jobs/CV and Publications/CV/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029E68A0-E0DF-274F-8585-EB4B7ACBED2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B5A8E0-6DAA-454B-8D85-881CFC3019D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28640" yWindow="4000" windowWidth="32100" windowHeight="18620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19100" yWindow="4000" windowWidth="32100" windowHeight="18620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,6 @@
     <t>Number of papers</t>
   </si>
   <si>
-    <t>Seconday author - Minor contribution (&lt;3 months)</t>
-  </si>
-  <si>
-    <t>Seconday author - Major contribution  (&gt;3 months)</t>
-  </si>
-  <si>
     <t>Senior, Co-senior or primary supervisor</t>
   </si>
   <si>
@@ -49,6 +43,12 @@
   </si>
   <si>
     <t>Total Papers</t>
+  </si>
+  <si>
+    <t>Seconday author - Major contribution</t>
+  </si>
+  <si>
+    <t>Seconday author - Minor contribution</t>
   </si>
 </sst>
 </file>
@@ -383,10 +383,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -399,7 +399,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -407,15 +407,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -423,7 +423,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7">
         <v>5</v>
